--- a/artfynd/A 3635-2021 artfynd.xlsx
+++ b/artfynd/A 3635-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3635-2021 artfynd.xlsx
+++ b/artfynd/A 3635-2021 artfynd.xlsx
@@ -2360,7 +2360,7 @@
         <v>126859596</v>
       </c>
       <c r="B15" t="n">
-        <v>91699</v>
+        <v>91773</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>126858689</v>
       </c>
       <c r="B16" t="n">
-        <v>79450</v>
+        <v>79481</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>126859418</v>
       </c>
       <c r="B19" t="n">
-        <v>91298</v>
+        <v>91372</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>126858508</v>
       </c>
       <c r="B20" t="n">
-        <v>82792</v>
+        <v>82852</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 3635-2021 artfynd.xlsx
+++ b/artfynd/A 3635-2021 artfynd.xlsx
@@ -2360,7 +2360,7 @@
         <v>126859596</v>
       </c>
       <c r="B15" t="n">
-        <v>91773</v>
+        <v>91779</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>126858689</v>
       </c>
       <c r="B16" t="n">
-        <v>79481</v>
+        <v>79484</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>126859418</v>
       </c>
       <c r="B19" t="n">
-        <v>91372</v>
+        <v>91378</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>126858508</v>
       </c>
       <c r="B20" t="n">
-        <v>82852</v>
+        <v>82855</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 3635-2021 artfynd.xlsx
+++ b/artfynd/A 3635-2021 artfynd.xlsx
@@ -2761,10 +2761,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126859410</v>
+        <v>126859418</v>
       </c>
       <c r="B18" t="n">
-        <v>8458</v>
+        <v>91378</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2772,32 +2772,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>101987</v>
+        <v>5321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aspvedborre</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Heteroborips cryptographus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ratzeburg, 1837)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2898,10 +2892,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126859418</v>
+        <v>126859410</v>
       </c>
       <c r="B19" t="n">
-        <v>91378</v>
+        <v>8458</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2909,26 +2903,32 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5321</v>
+        <v>101987</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Aspvedborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Heteroborips cryptographus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ratzeburg, 1837)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>

--- a/artfynd/A 3635-2021 artfynd.xlsx
+++ b/artfynd/A 3635-2021 artfynd.xlsx
@@ -2360,7 +2360,7 @@
         <v>126859596</v>
       </c>
       <c r="B15" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2488,10 +2488,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126858689</v>
+        <v>126859377</v>
       </c>
       <c r="B16" t="n">
-        <v>79484</v>
+        <v>40036</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2499,26 +2499,32 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1797</v>
+        <v>101166</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Mindre träfjäril</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Acossus terebra</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2526,10 +2532,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509182</v>
+        <v>509208</v>
       </c>
       <c r="R16" t="n">
-        <v>6663541</v>
+        <v>6663371</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2561,7 +2567,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2571,7 +2577,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2584,29 +2590,24 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Populus tremula</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2624,10 +2625,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126859377</v>
+        <v>126858689</v>
       </c>
       <c r="B17" t="n">
-        <v>40036</v>
+        <v>79484</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2635,32 +2636,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>101166</v>
+        <v>1797</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre träfjäril</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Acossus terebra</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2668,10 +2663,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509208</v>
+        <v>509182</v>
       </c>
       <c r="R17" t="n">
-        <v>6663371</v>
+        <v>6663541</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2703,7 +2698,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2713,7 +2708,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2726,24 +2721,29 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Populus tremula</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2764,7 +2764,7 @@
         <v>126859418</v>
       </c>
       <c r="B18" t="n">
-        <v>91378</v>
+        <v>91379</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 3635-2021 artfynd.xlsx
+++ b/artfynd/A 3635-2021 artfynd.xlsx
@@ -2761,10 +2761,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126859418</v>
+        <v>126859410</v>
       </c>
       <c r="B18" t="n">
-        <v>91379</v>
+        <v>8458</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2772,26 +2772,32 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5321</v>
+        <v>101987</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Aspvedborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Heteroborips cryptographus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ratzeburg, 1837)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2892,10 +2898,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126859410</v>
+        <v>126859418</v>
       </c>
       <c r="B19" t="n">
-        <v>8458</v>
+        <v>91379</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2903,32 +2909,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>101987</v>
+        <v>5321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aspvedborre</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Heteroborips cryptographus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ratzeburg, 1837)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>

--- a/artfynd/A 3635-2021 artfynd.xlsx
+++ b/artfynd/A 3635-2021 artfynd.xlsx
@@ -2488,10 +2488,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126859377</v>
+        <v>126858689</v>
       </c>
       <c r="B16" t="n">
-        <v>40036</v>
+        <v>79484</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2499,32 +2499,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>101166</v>
+        <v>1797</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre träfjäril</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Acossus terebra</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2532,10 +2526,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509208</v>
+        <v>509182</v>
       </c>
       <c r="R16" t="n">
-        <v>6663371</v>
+        <v>6663541</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2567,7 +2561,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2577,7 +2571,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2590,24 +2584,29 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Populus tremula</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2625,10 +2624,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126858689</v>
+        <v>126859377</v>
       </c>
       <c r="B17" t="n">
-        <v>79484</v>
+        <v>40036</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2636,26 +2635,32 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1797</v>
+        <v>101166</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Mindre träfjäril</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Acossus terebra</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2663,10 +2668,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509182</v>
+        <v>509208</v>
       </c>
       <c r="R17" t="n">
-        <v>6663541</v>
+        <v>6663371</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2698,7 +2703,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2708,7 +2713,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2721,29 +2726,24 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Populus tremula</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2761,10 +2761,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126859410</v>
+        <v>126859418</v>
       </c>
       <c r="B18" t="n">
-        <v>8458</v>
+        <v>91379</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2772,32 +2772,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>101987</v>
+        <v>5321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aspvedborre</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Heteroborips cryptographus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ratzeburg, 1837)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2898,10 +2892,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126859418</v>
+        <v>126859410</v>
       </c>
       <c r="B19" t="n">
-        <v>91379</v>
+        <v>8458</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2909,26 +2903,32 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5321</v>
+        <v>101987</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Aspvedborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Heteroborips cryptographus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ratzeburg, 1837)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>

--- a/artfynd/A 3635-2021 artfynd.xlsx
+++ b/artfynd/A 3635-2021 artfynd.xlsx
@@ -2360,7 +2360,7 @@
         <v>126859596</v>
       </c>
       <c r="B15" t="n">
-        <v>91780</v>
+        <v>91784</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>126858689</v>
       </c>
       <c r="B16" t="n">
-        <v>79484</v>
+        <v>79488</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>126859377</v>
       </c>
       <c r="B17" t="n">
-        <v>40036</v>
+        <v>40040</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>126859418</v>
       </c>
       <c r="B18" t="n">
-        <v>91379</v>
+        <v>91383</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>126859410</v>
       </c>
       <c r="B19" t="n">
-        <v>8458</v>
+        <v>8461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>126858508</v>
       </c>
       <c r="B20" t="n">
-        <v>82855</v>
+        <v>82859</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 3635-2021 artfynd.xlsx
+++ b/artfynd/A 3635-2021 artfynd.xlsx
@@ -2488,10 +2488,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126858689</v>
+        <v>126859377</v>
       </c>
       <c r="B16" t="n">
-        <v>79488</v>
+        <v>40040</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2499,26 +2499,32 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1797</v>
+        <v>101166</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Mindre träfjäril</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Acossus terebra</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2526,10 +2532,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509182</v>
+        <v>509208</v>
       </c>
       <c r="R16" t="n">
-        <v>6663541</v>
+        <v>6663371</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2561,7 +2567,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2571,7 +2577,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2584,29 +2590,24 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Populus tremula</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2624,10 +2625,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126859377</v>
+        <v>126858689</v>
       </c>
       <c r="B17" t="n">
-        <v>40040</v>
+        <v>79488</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2635,32 +2636,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>101166</v>
+        <v>1797</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre träfjäril</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Acossus terebra</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2668,10 +2663,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509208</v>
+        <v>509182</v>
       </c>
       <c r="R17" t="n">
-        <v>6663371</v>
+        <v>6663541</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2703,7 +2698,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2713,7 +2708,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2726,24 +2721,29 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Populus tremula</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>

--- a/artfynd/A 3635-2021 artfynd.xlsx
+++ b/artfynd/A 3635-2021 artfynd.xlsx
@@ -2488,10 +2488,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126859377</v>
+        <v>126858689</v>
       </c>
       <c r="B16" t="n">
-        <v>40040</v>
+        <v>79488</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2499,32 +2499,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>101166</v>
+        <v>1797</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre träfjäril</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Acossus terebra</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2532,10 +2526,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509208</v>
+        <v>509182</v>
       </c>
       <c r="R16" t="n">
-        <v>6663371</v>
+        <v>6663541</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2567,7 +2561,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2577,7 +2571,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2590,24 +2584,29 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Populus tremula</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2625,10 +2624,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126858689</v>
+        <v>126859377</v>
       </c>
       <c r="B17" t="n">
-        <v>79488</v>
+        <v>40040</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2636,26 +2635,32 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1797</v>
+        <v>101166</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Mindre träfjäril</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Acossus terebra</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2663,10 +2668,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509182</v>
+        <v>509208</v>
       </c>
       <c r="R17" t="n">
-        <v>6663541</v>
+        <v>6663371</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2698,7 +2703,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2708,7 +2713,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2721,29 +2726,24 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Populus tremula</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>

--- a/artfynd/A 3635-2021 artfynd.xlsx
+++ b/artfynd/A 3635-2021 artfynd.xlsx
@@ -2360,7 +2360,7 @@
         <v>126859596</v>
       </c>
       <c r="B15" t="n">
-        <v>91784</v>
+        <v>91773</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>126858689</v>
       </c>
       <c r="B16" t="n">
-        <v>79488</v>
+        <v>79481</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>126859377</v>
       </c>
       <c r="B17" t="n">
-        <v>40040</v>
+        <v>40036</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2761,10 +2761,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126859418</v>
+        <v>126859410</v>
       </c>
       <c r="B18" t="n">
-        <v>91383</v>
+        <v>8458</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2772,26 +2772,32 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5321</v>
+        <v>101987</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Aspvedborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Heteroborips cryptographus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ratzeburg, 1837)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2892,10 +2898,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126859410</v>
+        <v>126859418</v>
       </c>
       <c r="B19" t="n">
-        <v>8461</v>
+        <v>91372</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2903,32 +2909,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>101987</v>
+        <v>5321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aspvedborre</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Heteroborips cryptographus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ratzeburg, 1837)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>126858508</v>
       </c>
       <c r="B20" t="n">
-        <v>82859</v>
+        <v>82852</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 3635-2021 artfynd.xlsx
+++ b/artfynd/A 3635-2021 artfynd.xlsx
@@ -2360,7 +2360,7 @@
         <v>126859596</v>
       </c>
       <c r="B15" t="n">
-        <v>91773</v>
+        <v>91784</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>126858689</v>
       </c>
       <c r="B16" t="n">
-        <v>79481</v>
+        <v>79488</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>126859377</v>
       </c>
       <c r="B17" t="n">
-        <v>40036</v>
+        <v>40040</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2761,10 +2761,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126859410</v>
+        <v>126859418</v>
       </c>
       <c r="B18" t="n">
-        <v>8458</v>
+        <v>91383</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2772,32 +2772,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>101987</v>
+        <v>5321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aspvedborre</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Heteroborips cryptographus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ratzeburg, 1837)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2898,10 +2892,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126859418</v>
+        <v>126859410</v>
       </c>
       <c r="B19" t="n">
-        <v>91372</v>
+        <v>8461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2909,26 +2903,32 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5321</v>
+        <v>101987</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Aspvedborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Heteroborips cryptographus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ratzeburg, 1837)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>126858508</v>
       </c>
       <c r="B20" t="n">
-        <v>82852</v>
+        <v>82859</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
